--- a/backend/Customer_category.xlsx
+++ b/backend/Customer_category.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3"/>
+  <dimension ref="A1:E10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
   <cols>
     <col width="10.36328125" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -527,6 +527,191 @@
         </is>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Credit</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>aiyaz4</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Important Expenses / Payments</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>non_default</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Credit</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Refund/Reversal</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Others</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Credit</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>aq1</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>non_default</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Credit</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>aq2</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>non_default</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Credit</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>poojan1</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Other Expenses / Payments</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>non_default</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Credit</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>aq1</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>non_default</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Credit</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>aq2</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Important Expenses / Payments</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>non_default</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/backend/Customer_category.xlsx
+++ b/backend/Customer_category.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E10"/>
+  <dimension ref="A1:E13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
   <cols>
     <col width="10.36328125" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -712,6 +712,87 @@
         </is>
       </c>
     </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Credit</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>test1</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Important Expenses / Payments</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>non_default</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Credit</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>test2</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>non_default</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Credit</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>test3</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>non_default</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
